--- a/order_forms/031_fresh_produce_delivery_form--order_forms.xlsx
+++ b/order_forms/031_fresh_produce_delivery_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>customer_phone</t>
+          <t>customer_phone_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Customer Phone</t>
+          <t>Customer Phone 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>payment_method_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Payment Method</t>
+          <t>Payment Method 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>customer_email</t>
+          <t>customer_email_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Customer E-mail</t>
+          <t>Customer Email 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>customer_phone</t>
+          <t>customer_phone_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Customer Phone</t>
+          <t>Customer Phone 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>delivery_status</t>
+          <t>delivery_status_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Delivery Status</t>
+          <t>Delivery Status 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'credit'}</t>
+          <t>credit</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Credit'}</t>
+          <t>Credit</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'scheduled'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Scheduled'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'delivered'}</t>
+          <t>delivered</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Delivered'}</t>
+          <t>Delivered</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'single_pick_up'}</t>
+          <t>single_pick_up</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Single Pick Up'}</t>
+          <t>Single Pick Up</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'subscription_order'}</t>
+          <t>subscription_order</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Subscription Order'}</t>
+          <t>Subscription Order</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'one_time_order'}</t>
+          <t>one_time_order</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'One Time Order'}</t>
+          <t>One Time Order</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'multiple_orders'}</t>
+          <t>multiple_orders</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Multiple Orders'}</t>
+          <t>Multiple Orders</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'one_time'}</t>
+          <t>one_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'One Time'}</t>
+          <t>One Time</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'bi-weekly'}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Bi-Weekly'}</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1403,63 +1403,63 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'yearly'}</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Yearly'}</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'credit'}</t>
+          <t>credit</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Credit'}</t>
+          <t>Credit</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'pickup'}</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Pickup'}</t>
+          <t>Pickup</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'delivery'}</t>
+          <t>delivery</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Delivery'}</t>
+          <t>Delivery</t>
         </is>
       </c>
     </row>
@@ -1505,80 +1505,80 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'in_store_pickup'}</t>
+          <t>in_store_pickup</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'In Store Pickup'}</t>
+          <t>In Store Pickup</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>delivery_status_choices</t>
+          <t>delivery_status_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'scheduled'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Scheduled'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>delivery_status_choices</t>
+          <t>delivery_status_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>delivery_status_choices</t>
+          <t>delivery_status_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'delivered'}</t>
+          <t>delivered</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Delivered'}</t>
+          <t>Delivered</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>delivery_status_choices</t>
+          <t>delivery_status_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
